--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/post FET_HRM-2031-0392/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.76161</v>
+        <v>17.18765</v>
       </c>
       <c r="D2" t="n">
-        <v>16.61914</v>
+        <v>16.56473</v>
       </c>
       <c r="E2" t="n">
-        <v>16.45505</v>
+        <v>16.90231</v>
       </c>
       <c r="F2" t="n">
-        <v>42.74697</v>
+        <v>42.49979</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04986</v>
+        <v>0.05061</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80692</v>
+        <v>1.83666</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.02734</v>
+        <v>16.9736</v>
       </c>
       <c r="D3" t="n">
-        <v>16.71461</v>
+        <v>16.46529</v>
       </c>
       <c r="E3" t="n">
-        <v>16.35018</v>
+        <v>16.77883</v>
       </c>
       <c r="F3" t="n">
-        <v>43.37727</v>
+        <v>42.65033</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05056</v>
+        <v>0.05147</v>
       </c>
       <c r="H3" t="n">
-        <v>1.844</v>
+        <v>1.8644</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.87741</v>
+        <v>16.98876</v>
       </c>
       <c r="D4" t="n">
-        <v>16.83509</v>
+        <v>16.6345</v>
       </c>
       <c r="E4" t="n">
-        <v>16.87917</v>
+        <v>16.70549</v>
       </c>
       <c r="F4" t="n">
-        <v>42.65811</v>
+        <v>42.56079</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05077</v>
+        <v>0.05181</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83347</v>
+        <v>1.85868</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8655</v>
+        <v>16.73185</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06604</v>
+        <v>16.00243</v>
       </c>
       <c r="E6" t="n">
-        <v>16.8629</v>
+        <v>16.55575</v>
       </c>
       <c r="F6" t="n">
-        <v>21.49328</v>
+        <v>21.86898</v>
       </c>
       <c r="G6" t="n">
-        <v>34.91915</v>
+        <v>34.33945</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.71026</v>
+        <v>16.98368</v>
       </c>
       <c r="D7" t="n">
-        <v>16.13308</v>
+        <v>16.23591</v>
       </c>
       <c r="E7" t="n">
-        <v>16.84009</v>
+        <v>16.33653</v>
       </c>
       <c r="F7" t="n">
-        <v>22.54738</v>
+        <v>21.2234</v>
       </c>
       <c r="G7" t="n">
-        <v>34.0025</v>
+        <v>33.92437</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.82368</v>
+        <v>16.59217</v>
       </c>
       <c r="D8" t="n">
-        <v>16.12277</v>
+        <v>16.18165</v>
       </c>
       <c r="E8" t="n">
-        <v>16.41351</v>
+        <v>16.26337</v>
       </c>
       <c r="F8" t="n">
-        <v>21.80743</v>
+        <v>21.88403</v>
       </c>
       <c r="G8" t="n">
-        <v>34.29119</v>
+        <v>35.06212</v>
       </c>
     </row>
   </sheetData>
